--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/101.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/101.xlsx
@@ -426,13 +426,13 @@
         <v>-15.47381088740563</v>
       </c>
       <c r="E2">
-        <v>-7.12197843331085</v>
+        <v>-9.289319678803906</v>
       </c>
       <c r="F2">
-        <v>-1.477310821510682</v>
+        <v>-2.102775676489548</v>
       </c>
       <c r="G2">
-        <v>-8.960760699270912</v>
+        <v>-11.49928701878406</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.18963454423601</v>
       </c>
       <c r="E3">
-        <v>-8.205035447829339</v>
+        <v>-10.00327889085322</v>
       </c>
       <c r="F3">
-        <v>-1.349695798844571</v>
+        <v>-1.793797819799143</v>
       </c>
       <c r="G3">
-        <v>-8.993501994654304</v>
+        <v>-10.40628392462936</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.73866490249029</v>
       </c>
       <c r="E4">
-        <v>-8.631522601397725</v>
+        <v>-11.02926354745303</v>
       </c>
       <c r="F4">
-        <v>-1.27022860341965</v>
+        <v>-1.92902967606556</v>
       </c>
       <c r="G4">
-        <v>-8.170662590322912</v>
+        <v>-10.01444775460122</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.31284291899913</v>
       </c>
       <c r="E5">
-        <v>-9.754117722477183</v>
+        <v>-12.0589977805312</v>
       </c>
       <c r="F5">
-        <v>-1.409225720500024</v>
+        <v>-1.746163905127513</v>
       </c>
       <c r="G5">
-        <v>-7.892616491570603</v>
+        <v>-9.052373425979164</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.904993627258051</v>
       </c>
       <c r="E6">
-        <v>-10.67463421943836</v>
+        <v>-11.69533867534524</v>
       </c>
       <c r="F6">
-        <v>-1.293586681966467</v>
+        <v>-1.943400223542257</v>
       </c>
       <c r="G6">
-        <v>-7.093560046393335</v>
+        <v>-8.894943743404662</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.558849953194438</v>
       </c>
       <c r="E7">
-        <v>-11.51613790191371</v>
+        <v>-12.78165619114925</v>
       </c>
       <c r="F7">
-        <v>-1.151957445654632</v>
+        <v>-1.605815095048311</v>
       </c>
       <c r="G7">
-        <v>-6.767951339878318</v>
+        <v>-9.168560332225425</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.269910469087963</v>
       </c>
       <c r="E8">
-        <v>-12.3638727646236</v>
+        <v>-13.0921736538552</v>
       </c>
       <c r="F8">
-        <v>-1.109592520563669</v>
+        <v>-1.997841698091404</v>
       </c>
       <c r="G8">
-        <v>-7.197623734874785</v>
+        <v>-8.119332581736511</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.042029213384</v>
       </c>
       <c r="E9">
-        <v>-13.0712113476737</v>
+        <v>-14.44270498563674</v>
       </c>
       <c r="F9">
-        <v>-1.157113200262345</v>
+        <v>-1.675720666008766</v>
       </c>
       <c r="G9">
-        <v>-5.558466700924364</v>
+        <v>-7.550186903170549</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.870120958812577</v>
       </c>
       <c r="E10">
-        <v>-13.91439962247989</v>
+        <v>-14.39097622704712</v>
       </c>
       <c r="F10">
-        <v>-1.040839887509655</v>
+        <v>-1.605206160123825</v>
       </c>
       <c r="G10">
-        <v>-4.993257261004594</v>
+        <v>-7.054816731947244</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.759740562180343</v>
       </c>
       <c r="E11">
-        <v>-15.08676720137766</v>
+        <v>-16.83027950754483</v>
       </c>
       <c r="F11">
-        <v>-1.278302336176561</v>
+        <v>-1.698077842417025</v>
       </c>
       <c r="G11">
-        <v>-4.078765403418479</v>
+        <v>-6.42567072602753</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.713273513530811</v>
       </c>
       <c r="E12">
-        <v>-15.53548916232371</v>
+        <v>-17.11891085537172</v>
       </c>
       <c r="F12">
-        <v>-0.7240765325389488</v>
+        <v>-1.603267704083327</v>
       </c>
       <c r="G12">
-        <v>-4.005138870625087</v>
+        <v>-5.553874974261395</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.725881315062465</v>
       </c>
       <c r="E13">
-        <v>-15.37741824861197</v>
+        <v>-17.62060237678548</v>
       </c>
       <c r="F13">
-        <v>-0.8254059962735533</v>
+        <v>-1.512156310915138</v>
       </c>
       <c r="G13">
-        <v>-2.999981102354952</v>
+        <v>-5.273544599086989</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.7961652499840495</v>
       </c>
       <c r="E14">
-        <v>-17.4566625607598</v>
+        <v>-19.52743862651329</v>
       </c>
       <c r="F14">
-        <v>-1.014337360867733</v>
+        <v>-1.396921117390018</v>
       </c>
       <c r="G14">
-        <v>-2.426928980052649</v>
+        <v>-4.270889603244543</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.08184923852044068</v>
       </c>
       <c r="E15">
-        <v>-18.65505527977965</v>
+        <v>-19.75840891480052</v>
       </c>
       <c r="F15">
-        <v>-0.655133854775081</v>
+        <v>-1.287619278077091</v>
       </c>
       <c r="G15">
-        <v>-1.800322162561555</v>
+        <v>-3.440796793636606</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.9095915937826161</v>
       </c>
       <c r="E16">
-        <v>-17.6579849297188</v>
+        <v>-20.08678215051872</v>
       </c>
       <c r="F16">
-        <v>-0.446324605383263</v>
+        <v>-1.274240130503459</v>
       </c>
       <c r="G16">
-        <v>-1.360486392759525</v>
+        <v>-3.344764488633428</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.682161685735405</v>
       </c>
       <c r="E17">
-        <v>-20.91785222888039</v>
+        <v>-21.53132007422548</v>
       </c>
       <c r="F17">
-        <v>-0.4729554122043351</v>
+        <v>-1.145274206691478</v>
       </c>
       <c r="G17">
-        <v>-1.356507117021321</v>
+        <v>-2.366951826517672</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.376320059312804</v>
       </c>
       <c r="E18">
-        <v>-20.37072652774766</v>
+        <v>-22.93080873850394</v>
       </c>
       <c r="F18">
-        <v>-0.5729434770285623</v>
+        <v>-0.9911313180887987</v>
       </c>
       <c r="G18">
-        <v>-0.4150707292910768</v>
+        <v>-2.862338550468674</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.960771742727608</v>
       </c>
       <c r="E19">
-        <v>-22.14492377379081</v>
+        <v>-22.78483337886669</v>
       </c>
       <c r="F19">
-        <v>-0.467779861272679</v>
+        <v>-0.9445085996441769</v>
       </c>
       <c r="G19">
-        <v>0.005441386198227918</v>
+        <v>-1.727400775968029</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.399380274717661</v>
       </c>
       <c r="E20">
-        <v>-21.80925969492026</v>
+        <v>-23.45051000104622</v>
       </c>
       <c r="F20">
-        <v>-0.2828006347904783</v>
+        <v>-0.7102301917202617</v>
       </c>
       <c r="G20">
-        <v>0.1540650176382686</v>
+        <v>-0.7774298018375438</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.658216969053644</v>
       </c>
       <c r="E21">
-        <v>-22.40251243229512</v>
+        <v>-23.8532045521783</v>
       </c>
       <c r="F21">
-        <v>0.1963448388079801</v>
+        <v>-0.4966658653173368</v>
       </c>
       <c r="G21">
-        <v>-0.09753313280080235</v>
+        <v>-1.053704758726342</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.711999896394392</v>
       </c>
       <c r="E22">
-        <v>-24.25598967279054</v>
+        <v>-24.28275748264988</v>
       </c>
       <c r="F22">
-        <v>0.2307864832039996</v>
+        <v>-0.2329036043656854</v>
       </c>
       <c r="G22">
-        <v>0.09313111644244312</v>
+        <v>-1.274776368747794</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.556434451276673</v>
       </c>
       <c r="E23">
-        <v>-24.28760294983809</v>
+        <v>-25.35333855127724</v>
       </c>
       <c r="F23">
-        <v>-0.02150182839029303</v>
+        <v>-0.5659498317059817</v>
       </c>
       <c r="G23">
-        <v>-0.1184723333366926</v>
+        <v>-1.325550205683596</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.209559247971999</v>
       </c>
       <c r="E24">
-        <v>-23.5365193078739</v>
+        <v>-26.0780755314648</v>
       </c>
       <c r="F24">
-        <v>-0.1824451501938691</v>
+        <v>-0.7659053731775355</v>
       </c>
       <c r="G24">
-        <v>0.3962545976547308</v>
+        <v>-1.444521280728384</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.70470207165921</v>
       </c>
       <c r="E25">
-        <v>-23.01273336177671</v>
+        <v>-26.59706129511387</v>
       </c>
       <c r="F25">
-        <v>-0.3341451724219829</v>
+        <v>-0.2759629845005685</v>
       </c>
       <c r="G25">
-        <v>0.02559929798685017</v>
+        <v>-2.068453177423747</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.085743168670131</v>
       </c>
       <c r="E26">
-        <v>-24.04958635599494</v>
+        <v>-26.10530071719892</v>
       </c>
       <c r="F26">
-        <v>0.01101244590663655</v>
+        <v>-1.261324216910092</v>
       </c>
       <c r="G26">
-        <v>-0.1083023374400515</v>
+        <v>-1.400964433068193</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.40143752077664</v>
       </c>
       <c r="E27">
-        <v>-24.40768449509948</v>
+        <v>-24.87818388754842</v>
       </c>
       <c r="F27">
-        <v>-0.05864844248988299</v>
+        <v>-0.6121536599359698</v>
       </c>
       <c r="G27">
-        <v>-0.2967981793550744</v>
+        <v>-2.029173554600294</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.7003648147909869</v>
       </c>
       <c r="E28">
-        <v>-24.010659593425</v>
+        <v>-25.89671920440562</v>
       </c>
       <c r="F28">
-        <v>0.1093011942835972</v>
+        <v>-0.7536071048911904</v>
       </c>
       <c r="G28">
-        <v>-0.3259905699203677</v>
+        <v>-2.605966593361973</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.023354534423146</v>
       </c>
       <c r="E29">
-        <v>-23.98472502278307</v>
+        <v>-25.66488397758294</v>
       </c>
       <c r="F29">
-        <v>-0.1556923980173083</v>
+        <v>-0.4483176992778436</v>
       </c>
       <c r="G29">
-        <v>-0.6779644611101411</v>
+        <v>-1.529853902548639</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.5967532645042243</v>
       </c>
       <c r="E30">
-        <v>-23.73772846498271</v>
+        <v>-25.21618465900693</v>
       </c>
       <c r="F30">
-        <v>-0.06926164768220044</v>
+        <v>-0.5008793149053634</v>
       </c>
       <c r="G30">
-        <v>-0.2098500113116559</v>
+        <v>-2.347770525663135</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.140163658389972</v>
       </c>
       <c r="E31">
-        <v>-23.51468300620892</v>
+        <v>-25.39984597933601</v>
       </c>
       <c r="F31">
-        <v>-0.14025601645952</v>
+        <v>-0.8803281255680355</v>
       </c>
       <c r="G31">
-        <v>0.4510838528761402</v>
+        <v>-1.966514859178508</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.601950958316549</v>
       </c>
       <c r="E32">
-        <v>-23.53948545834892</v>
+        <v>-25.37613488943185</v>
       </c>
       <c r="F32">
-        <v>-0.2454576411573739</v>
+        <v>-0.5038448042320238</v>
       </c>
       <c r="G32">
-        <v>-0.791324161465865</v>
+        <v>-1.828491594555214</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.991539206264874</v>
       </c>
       <c r="E33">
-        <v>-22.40858058746539</v>
+        <v>-24.7707820695085</v>
       </c>
       <c r="F33">
-        <v>-0.4139235660592874</v>
+        <v>-0.7016045374518207</v>
       </c>
       <c r="G33">
-        <v>-0.408029198929047</v>
+        <v>-1.256154550089393</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.323903894221612</v>
       </c>
       <c r="E34">
-        <v>-22.31885793195142</v>
+        <v>-23.23344665643656</v>
       </c>
       <c r="F34">
-        <v>-0.3104743119568673</v>
+        <v>-0.5683443950501261</v>
       </c>
       <c r="G34">
-        <v>-0.442760132181541</v>
+        <v>-2.288074768498997</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.617724752502419</v>
       </c>
       <c r="E35">
-        <v>-21.46529945166766</v>
+        <v>-24.07609604283584</v>
       </c>
       <c r="F35">
-        <v>-0.306833372057272</v>
+        <v>-0.8750686382228612</v>
       </c>
       <c r="G35">
-        <v>-0.4725815263992958</v>
+        <v>-2.091017855819419</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.892901423630849</v>
       </c>
       <c r="E36">
-        <v>-20.98607821827995</v>
+        <v>-23.19265416257546</v>
       </c>
       <c r="F36">
-        <v>-0.2506862462371972</v>
+        <v>-0.3208072012021519</v>
       </c>
       <c r="G36">
-        <v>-0.1507733261633616</v>
+        <v>-1.886220887669025</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.167676459221368</v>
       </c>
       <c r="E37">
-        <v>-20.20542816951968</v>
+        <v>-22.98890453154835</v>
       </c>
       <c r="F37">
-        <v>-0.1488887974045804</v>
+        <v>-0.5025271609103782</v>
       </c>
       <c r="G37">
-        <v>0.3438287984948323</v>
+        <v>-1.66657281222946</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.452887388774665</v>
       </c>
       <c r="E38">
-        <v>-20.02391334587023</v>
+        <v>-22.04367162345331</v>
       </c>
       <c r="F38">
-        <v>-0.1230047079226381</v>
+        <v>-0.7630364899117169</v>
       </c>
       <c r="G38">
-        <v>0.02518547979444128</v>
+        <v>-2.884999234684985</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.751879436204586</v>
       </c>
       <c r="E39">
-        <v>-19.04481198067182</v>
+        <v>-22.15427960109065</v>
       </c>
       <c r="F39">
-        <v>-0.03808877229564808</v>
+        <v>-0.2717194445001485</v>
       </c>
       <c r="G39">
-        <v>-0.1168303027492141</v>
+        <v>-1.687502081128732</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.062667412803199</v>
       </c>
       <c r="E40">
-        <v>-18.1036682846057</v>
+        <v>-20.883381484734</v>
       </c>
       <c r="F40">
-        <v>0.2313526580687691</v>
+        <v>-0.2945438141534619</v>
       </c>
       <c r="G40">
-        <v>-0.5427617812863058</v>
+        <v>-2.197931924010182</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.38166338230882</v>
       </c>
       <c r="E41">
-        <v>-18.1220855883949</v>
+        <v>-20.27819621834893</v>
       </c>
       <c r="F41">
-        <v>-0.002722243645012062</v>
+        <v>-0.3137509994959115</v>
       </c>
       <c r="G41">
-        <v>-0.05105307342943489</v>
+        <v>-2.562270702789133</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.70344477964975</v>
       </c>
       <c r="E42">
-        <v>-18.51771572007502</v>
+        <v>-20.55561959300683</v>
       </c>
       <c r="F42">
-        <v>0.1926096684064162</v>
+        <v>-0.2272996609839029</v>
       </c>
       <c r="G42">
-        <v>-0.9453075661339857</v>
+        <v>-2.045242942647916</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.021129738217721</v>
       </c>
       <c r="E43">
-        <v>-16.96964782360489</v>
+        <v>-19.1221402028268</v>
       </c>
       <c r="F43">
-        <v>0.4947174088356452</v>
+        <v>-0.4248115442279336</v>
       </c>
       <c r="G43">
-        <v>-0.9563714093262301</v>
+        <v>-3.596452023802059</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.329485342023975</v>
       </c>
       <c r="E44">
-        <v>-16.01577458710322</v>
+        <v>-18.79997097649911</v>
       </c>
       <c r="F44">
-        <v>0.3650863285391801</v>
+        <v>-0.1051262518432422</v>
       </c>
       <c r="G44">
-        <v>-0.5824154957556961</v>
+        <v>-3.117644511911728</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.627684012317109</v>
       </c>
       <c r="E45">
-        <v>-15.78076037152715</v>
+        <v>-17.46749467058615</v>
       </c>
       <c r="F45">
-        <v>0.1392253175558256</v>
+        <v>-0.2128760593590381</v>
       </c>
       <c r="G45">
-        <v>-2.07206829315263</v>
+        <v>-3.31027853575084</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.916096748349236</v>
       </c>
       <c r="E46">
-        <v>-15.01251381307389</v>
+        <v>-18.17681672525161</v>
       </c>
       <c r="F46">
-        <v>0.1301308863364146</v>
+        <v>0.1662156256197024</v>
       </c>
       <c r="G46">
-        <v>-2.383613802216824</v>
+        <v>-4.232099941160902</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.19515794685832</v>
       </c>
       <c r="E47">
-        <v>-14.37786629479492</v>
+        <v>-17.06254041092424</v>
       </c>
       <c r="F47">
-        <v>0.3968206276727558</v>
+        <v>-0.462213926832867</v>
       </c>
       <c r="G47">
-        <v>-2.306478091151805</v>
+        <v>-4.452718006443473</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.468524323616966</v>
       </c>
       <c r="E48">
-        <v>-13.5253357781109</v>
+        <v>-16.92778660987799</v>
       </c>
       <c r="F48">
-        <v>0.4342760644258564</v>
+        <v>-0.003379481599919432</v>
       </c>
       <c r="G48">
-        <v>-2.012127555618587</v>
+        <v>-4.74340045751918</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.742261349162394</v>
       </c>
       <c r="E49">
-        <v>-13.27039174842707</v>
+        <v>-16.06748523179681</v>
       </c>
       <c r="F49">
-        <v>0.8364534305339578</v>
+        <v>0.1747929768577224</v>
       </c>
       <c r="G49">
-        <v>-2.381696996349586</v>
+        <v>-4.934207060220614</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.020656340159378</v>
       </c>
       <c r="E50">
-        <v>-12.49480000513337</v>
+        <v>-15.20941186292739</v>
       </c>
       <c r="F50">
-        <v>0.2459409651088396</v>
+        <v>-0.1792959509810178</v>
       </c>
       <c r="G50">
-        <v>-2.794846458559552</v>
+        <v>-4.689282969588714</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.305445637504461</v>
       </c>
       <c r="E51">
-        <v>-12.20663961860328</v>
+        <v>-14.7689271962013</v>
       </c>
       <c r="F51">
-        <v>0.2806724276873844</v>
+        <v>0.06569226819605663</v>
       </c>
       <c r="G51">
-        <v>-2.909659488407016</v>
+        <v>-4.519978360164846</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.600421945797474</v>
       </c>
       <c r="E52">
-        <v>-11.64424390311669</v>
+        <v>-14.35965277233607</v>
       </c>
       <c r="F52">
-        <v>0.3950310399883092</v>
+        <v>0.118769380099052</v>
       </c>
       <c r="G52">
-        <v>-3.464156002961704</v>
+        <v>-4.486369701850164</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.908372019685638</v>
       </c>
       <c r="E53">
-        <v>-11.57483145352712</v>
+        <v>-14.47087209396445</v>
       </c>
       <c r="F53">
-        <v>0.2030074895942339</v>
+        <v>0.09566865376349448</v>
       </c>
       <c r="G53">
-        <v>-3.73930868491269</v>
+        <v>-5.273703505272874</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.228126963141593</v>
       </c>
       <c r="E54">
-        <v>-10.42855241338755</v>
+        <v>-13.08876371292743</v>
       </c>
       <c r="F54">
-        <v>0.2996262200833637</v>
+        <v>0.1020525723086309</v>
       </c>
       <c r="G54">
-        <v>-3.429064220245429</v>
+        <v>-5.79478006260862</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.555246422672628</v>
       </c>
       <c r="E55">
-        <v>-10.01210035822016</v>
+        <v>-12.16563428646383</v>
       </c>
       <c r="F55">
-        <v>0.2749932582746186</v>
+        <v>-0.1102725042154627</v>
       </c>
       <c r="G55">
-        <v>-4.343268060369629</v>
+        <v>-5.537295762200724</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.887444623726886</v>
       </c>
       <c r="E56">
-        <v>-9.949399107109953</v>
+        <v>-11.49255813775576</v>
       </c>
       <c r="F56">
-        <v>0.1328041819216764</v>
+        <v>-0.2524354494208001</v>
       </c>
       <c r="G56">
-        <v>-4.298526037406378</v>
+        <v>-5.160419947464553</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.22243596106707</v>
       </c>
       <c r="E57">
-        <v>-9.479674083716329</v>
+        <v>-12.20530371877102</v>
       </c>
       <c r="F57">
-        <v>0.7220338455552886</v>
+        <v>-0.3179866209667543</v>
       </c>
       <c r="G57">
-        <v>-4.401387997857073</v>
+        <v>-5.439704190248549</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.554447330738279</v>
       </c>
       <c r="E58">
-        <v>-9.127843352638397</v>
+        <v>-11.28949230630381</v>
       </c>
       <c r="F58">
-        <v>0.2087468398317865</v>
+        <v>-0.1940711353191101</v>
       </c>
       <c r="G58">
-        <v>-4.839260614154316</v>
+        <v>-5.525579741537244</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.873071362384001</v>
       </c>
       <c r="E59">
-        <v>-9.479121609887393</v>
+        <v>-10.62594406690789</v>
       </c>
       <c r="F59">
-        <v>0.2073001244780325</v>
+        <v>-0.1123020233460983</v>
       </c>
       <c r="G59">
-        <v>-4.702657573567369</v>
+        <v>-6.743284465065208</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.17372801171672</v>
       </c>
       <c r="E60">
-        <v>-8.632301498927044</v>
+        <v>-10.44747237779159</v>
       </c>
       <c r="F60">
-        <v>-0.1439357571540436</v>
+        <v>-0.1915411651191956</v>
       </c>
       <c r="G60">
-        <v>-4.932478955449114</v>
+        <v>-6.309874464154902</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.45005213400918</v>
       </c>
       <c r="E61">
-        <v>-8.301532700458786</v>
+        <v>-11.09498076225235</v>
       </c>
       <c r="F61">
-        <v>0.3341969365114914</v>
+        <v>-0.07643266806731026</v>
       </c>
       <c r="G61">
-        <v>-5.290805783528749</v>
+        <v>-6.023730771013536</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.69524974026089</v>
       </c>
       <c r="E62">
-        <v>-8.642336597328041</v>
+        <v>-10.12741794882548</v>
       </c>
       <c r="F62">
-        <v>0.199625485611813</v>
+        <v>-0.4095549132915477</v>
       </c>
       <c r="G62">
-        <v>-5.680258360768612</v>
+        <v>-6.129976109005367</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.90054968581673</v>
       </c>
       <c r="E63">
-        <v>-7.329613495036543</v>
+        <v>-11.06563172220863</v>
       </c>
       <c r="F63">
-        <v>0.2038183470229389</v>
+        <v>-0.6743750897947126</v>
       </c>
       <c r="G63">
-        <v>-5.609945684060031</v>
+        <v>-6.035453412768096</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.06455911420784</v>
       </c>
       <c r="E64">
-        <v>-7.791658226513158</v>
+        <v>-7.661813291291225</v>
       </c>
       <c r="F64">
-        <v>-0.02097049505566309</v>
+        <v>-0.3788674437680775</v>
       </c>
       <c r="G64">
-        <v>-5.733568075587495</v>
+        <v>-6.476057229135237</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.18533862774725</v>
       </c>
       <c r="E65">
-        <v>-7.23170788699071</v>
+        <v>-9.050442674899294</v>
       </c>
       <c r="F65">
-        <v>0.2303327514592261</v>
+        <v>-0.4421594588256573</v>
       </c>
       <c r="G65">
-        <v>-5.485657872879172</v>
+        <v>-7.653141558896343</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.25955296227238</v>
       </c>
       <c r="E66">
-        <v>-7.730342688449301</v>
+        <v>-9.123636400285271</v>
       </c>
       <c r="F66">
-        <v>-0.1912101705828688</v>
+        <v>-0.3381749121238186</v>
       </c>
       <c r="G66">
-        <v>-5.561333633361373</v>
+        <v>-7.212825759991119</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.28166842757739</v>
       </c>
       <c r="E67">
-        <v>-7.097402404871223</v>
+        <v>-8.511101420585755</v>
       </c>
       <c r="F67">
-        <v>-0.04166715581158351</v>
+        <v>-0.335320282211239</v>
       </c>
       <c r="G67">
-        <v>-5.513618740503857</v>
+        <v>-7.460600230332331</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.25211908657911</v>
       </c>
       <c r="E68">
-        <v>-5.913120410859278</v>
+        <v>-8.308479379586553</v>
       </c>
       <c r="F68">
-        <v>-0.1814038635544677</v>
+        <v>-0.5324789990361267</v>
       </c>
       <c r="G68">
-        <v>-6.31197666057234</v>
+        <v>-7.541923781504528</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.17348866001081</v>
       </c>
       <c r="E69">
-        <v>-7.420604123272664</v>
+        <v>-9.403459866167237</v>
       </c>
       <c r="F69">
-        <v>-0.121674394953669</v>
+        <v>-0.9374017193486424</v>
       </c>
       <c r="G69">
-        <v>-6.226011724554085</v>
+        <v>-7.93755714726621</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.04997573368992</v>
       </c>
       <c r="E70">
-        <v>-7.189285142486854</v>
+        <v>-8.558396803121864</v>
       </c>
       <c r="F70">
-        <v>-0.2596310172475992</v>
+        <v>-1.042324611805379</v>
       </c>
       <c r="G70">
-        <v>-6.606098768463349</v>
+        <v>-7.801834711792709</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.88627727553272</v>
       </c>
       <c r="E71">
-        <v>-6.34025966468477</v>
+        <v>-9.862946009829518</v>
       </c>
       <c r="F71">
-        <v>-0.475913774854376</v>
+        <v>-0.6552106645119798</v>
       </c>
       <c r="G71">
-        <v>-6.01776516795177</v>
+        <v>-7.913542449924337</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.69557643992503</v>
       </c>
       <c r="E72">
-        <v>-7.958038890028974</v>
+        <v>-8.159320502721906</v>
       </c>
       <c r="F72">
-        <v>-0.5001025071538404</v>
+        <v>-0.8318786023499543</v>
       </c>
       <c r="G72">
-        <v>-7.086915781496018</v>
+        <v>-7.650655339196351</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.49011376052576</v>
       </c>
       <c r="E73">
-        <v>-7.500201110905485</v>
+        <v>-8.708932336084843</v>
       </c>
       <c r="F73">
-        <v>-0.3734076176246</v>
+        <v>-1.015637583424309</v>
       </c>
       <c r="G73">
-        <v>-6.146581805430351</v>
+        <v>-8.048453801740717</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.27770431874508</v>
       </c>
       <c r="E74">
-        <v>-7.511789475891114</v>
+        <v>-9.685063022334218</v>
       </c>
       <c r="F74">
-        <v>-0.4851871648422316</v>
+        <v>-0.7738167760781132</v>
       </c>
       <c r="G74">
-        <v>-6.876845114301564</v>
+        <v>-8.1652664010939</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.06159655503813</v>
       </c>
       <c r="E75">
-        <v>-7.366357533134781</v>
+        <v>-9.04102344896334</v>
       </c>
       <c r="F75">
-        <v>-0.3865690056348595</v>
+        <v>-0.9805537462795787</v>
       </c>
       <c r="G75">
-        <v>-6.528764424665974</v>
+        <v>-6.875252741897175</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.8479222104342</v>
       </c>
       <c r="E76">
-        <v>-7.608843730823505</v>
+        <v>-10.62880606248074</v>
       </c>
       <c r="F76">
-        <v>-0.7489842673240227</v>
+        <v>-1.266053162773594</v>
       </c>
       <c r="G76">
-        <v>-5.713867019083293</v>
+        <v>-7.55504016293112</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.637206176309647</v>
       </c>
       <c r="E77">
-        <v>-9.222828094949282</v>
+        <v>-9.815890636415816</v>
       </c>
       <c r="F77">
-        <v>-0.7558266687316788</v>
+        <v>-1.029047613263292</v>
       </c>
       <c r="G77">
-        <v>-6.541082964617602</v>
+        <v>-7.282621991595573</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.42519854533468</v>
       </c>
       <c r="E78">
-        <v>-8.779834653622936</v>
+        <v>-11.01798311869993</v>
       </c>
       <c r="F78">
-        <v>-0.5221619468499964</v>
+        <v>-1.275396235821729</v>
       </c>
       <c r="G78">
-        <v>-6.216609775222555</v>
+        <v>-7.565362443922568</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.203249588781507</v>
       </c>
       <c r="E79">
-        <v>-9.236273134278056</v>
+        <v>-10.89677398341062</v>
       </c>
       <c r="F79">
-        <v>-0.8545160947052457</v>
+        <v>-1.03743808720329</v>
       </c>
       <c r="G79">
-        <v>-6.377028880419019</v>
+        <v>-7.330631523006084</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.96795501590973</v>
       </c>
       <c r="E80">
-        <v>-9.831527457164301</v>
+        <v>-11.00045792429024</v>
       </c>
       <c r="F80">
-        <v>-0.4461092213787633</v>
+        <v>-0.9029070208044557</v>
       </c>
       <c r="G80">
-        <v>-6.267860330716012</v>
+        <v>-7.366494662833008</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.712528674237754</v>
       </c>
       <c r="E81">
-        <v>-11.41533407050296</v>
+        <v>-12.45344145202131</v>
       </c>
       <c r="F81">
-        <v>-0.8356359446343343</v>
+        <v>-1.366473579312736</v>
       </c>
       <c r="G81">
-        <v>-6.00704231095007</v>
+        <v>-6.938421261332008</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.430181948080264</v>
       </c>
       <c r="E82">
-        <v>-11.52062561965531</v>
+        <v>-12.66137539303151</v>
       </c>
       <c r="F82">
-        <v>-0.6790391037156818</v>
+        <v>-1.197357543132535</v>
       </c>
       <c r="G82">
-        <v>-5.760191482814315</v>
+        <v>-6.989489736820806</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.115886025485365</v>
       </c>
       <c r="E83">
-        <v>-11.99741053402689</v>
+        <v>-12.85953235865915</v>
       </c>
       <c r="F83">
-        <v>-0.5613570845512073</v>
+        <v>-1.427177818904488</v>
       </c>
       <c r="G83">
-        <v>-5.897817481972896</v>
+        <v>-6.094298359728641</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.77473676089733</v>
       </c>
       <c r="E84">
-        <v>-12.72736884474529</v>
+        <v>-13.68564375798243</v>
       </c>
       <c r="F84">
-        <v>-0.3698696186095083</v>
+        <v>-1.16774461807269</v>
       </c>
       <c r="G84">
-        <v>-5.389274650048831</v>
+        <v>-6.870356445044592</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.413559251274569</v>
       </c>
       <c r="E85">
-        <v>-13.9834180948308</v>
+        <v>-14.84654524069277</v>
       </c>
       <c r="F85">
-        <v>-0.6159086266614768</v>
+        <v>-1.512326559301048</v>
       </c>
       <c r="G85">
-        <v>-5.763948952001387</v>
+        <v>-6.974820709536295</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.042159933931683</v>
       </c>
       <c r="E86">
-        <v>-16.20607012185354</v>
+        <v>-15.44727448865429</v>
       </c>
       <c r="F86">
-        <v>-0.4586070366104537</v>
+        <v>-1.330805354685209</v>
       </c>
       <c r="G86">
-        <v>-5.675127015182741</v>
+        <v>-6.245898171608487</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.673770975537375</v>
       </c>
       <c r="E87">
-        <v>-16.79212711403021</v>
+        <v>-17.95471771754541</v>
       </c>
       <c r="F87">
-        <v>-1.036261393708119</v>
+        <v>-1.571388495858489</v>
       </c>
       <c r="G87">
-        <v>-4.813723065864378</v>
+        <v>-5.747435950851503</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.326371531442641</v>
       </c>
       <c r="E88">
-        <v>-19.11734002037867</v>
+        <v>-19.37195347145994</v>
       </c>
       <c r="F88">
-        <v>-0.7902754398043177</v>
+        <v>-1.205097905794245</v>
       </c>
       <c r="G88">
-        <v>-4.516489045166454</v>
+        <v>-5.81521937076808</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.013764847127571</v>
       </c>
       <c r="E89">
-        <v>-20.1511227092197</v>
+        <v>-20.92356716307807</v>
       </c>
       <c r="F89">
-        <v>-0.6002465670107384</v>
+        <v>-1.133747203185952</v>
       </c>
       <c r="G89">
-        <v>-4.58746052043735</v>
+        <v>-5.750279709469736</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.744275014143755</v>
       </c>
       <c r="E90">
-        <v>-21.02644050711032</v>
+        <v>-21.78527689657563</v>
       </c>
       <c r="F90">
-        <v>-0.6321978338547293</v>
+        <v>-1.406064643492807</v>
       </c>
       <c r="G90">
-        <v>-4.59849456871974</v>
+        <v>-5.806410009088079</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.523286790014627</v>
       </c>
       <c r="E91">
-        <v>-23.00863056432576</v>
+        <v>-23.76968137758083</v>
       </c>
       <c r="F91">
-        <v>-0.5187680650732097</v>
+        <v>-1.241356852728231</v>
       </c>
       <c r="G91">
-        <v>-5.421267762140348</v>
+        <v>-5.643325914732502</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.353569594279537</v>
       </c>
       <c r="E92">
-        <v>-24.86531396441862</v>
+        <v>-25.98354816502869</v>
       </c>
       <c r="F92">
-        <v>-0.697419594570272</v>
+        <v>-1.52433738496374</v>
       </c>
       <c r="G92">
-        <v>-4.469965948703076</v>
+        <v>-5.214606956851344</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.230774007093258</v>
       </c>
       <c r="E93">
-        <v>-27.72125043904402</v>
+        <v>-28.40623194591825</v>
       </c>
       <c r="F93">
-        <v>-0.6713438766725615</v>
+        <v>-1.533206138090201</v>
       </c>
       <c r="G93">
-        <v>-4.683151839249984</v>
+        <v>-5.667036041884763</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.143181163953653</v>
       </c>
       <c r="E94">
-        <v>-29.63554055698846</v>
+        <v>-30.82744850122932</v>
       </c>
       <c r="F94">
-        <v>-0.707678049637531</v>
+        <v>-1.584505540103116</v>
       </c>
       <c r="G94">
-        <v>-4.847388003453227</v>
+        <v>-5.592982448716805</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.077711753578456</v>
       </c>
       <c r="E95">
-        <v>-32.00471588900339</v>
+        <v>-32.45060076098363</v>
       </c>
       <c r="F95">
-        <v>-0.6103870359872972</v>
+        <v>-1.228844784143302</v>
       </c>
       <c r="G95">
-        <v>-4.517058458999209</v>
+        <v>-5.622002690914057</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.017994963581433</v>
       </c>
       <c r="E96">
-        <v>-34.28409837415722</v>
+        <v>-34.06283260566843</v>
       </c>
       <c r="F96">
-        <v>-0.6159450518975319</v>
+        <v>-1.086386477784735</v>
       </c>
       <c r="G96">
-        <v>-4.829103860439832</v>
+        <v>-4.992826890084489</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.947218290640485</v>
       </c>
       <c r="E97">
-        <v>-36.8643707862767</v>
+        <v>-36.10916396872852</v>
       </c>
       <c r="F97">
-        <v>-0.8174146162242457</v>
+        <v>-1.581387223155616</v>
       </c>
       <c r="G97">
-        <v>-5.083628533135619</v>
+        <v>-6.126228571454912</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.845026175367861</v>
       </c>
       <c r="E98">
-        <v>-39.64354283376107</v>
+        <v>-38.2726786536851</v>
       </c>
       <c r="F98">
-        <v>-0.9198202081283913</v>
+        <v>-1.750124753622027</v>
       </c>
       <c r="G98">
-        <v>-4.77892261115556</v>
+        <v>-6.746896270248552</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.705318068703344</v>
       </c>
       <c r="E99">
-        <v>-41.4777672670129</v>
+        <v>-41.80421363704084</v>
       </c>
       <c r="F99">
-        <v>-0.8880035562872128</v>
+        <v>-1.669354960081658</v>
       </c>
       <c r="G99">
-        <v>-5.121653459199687</v>
+        <v>-6.302309867597668</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.522111822468561</v>
       </c>
       <c r="E100">
-        <v>-44.39363809512982</v>
+        <v>-44.36101043990455</v>
       </c>
       <c r="F100">
-        <v>-0.6036127339340049</v>
+        <v>-1.618329539192114</v>
       </c>
       <c r="G100">
-        <v>-5.530896477673314</v>
+        <v>-6.186122961351406</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.312958588598538</v>
       </c>
       <c r="E101">
-        <v>-46.25563339523368</v>
+        <v>-46.43440622787148</v>
       </c>
       <c r="F101">
-        <v>-0.6857595597678491</v>
+        <v>-1.870389797134583</v>
       </c>
       <c r="G101">
-        <v>-5.979948806256675</v>
+        <v>-6.766147092559414</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.077245323652748</v>
       </c>
       <c r="E102">
-        <v>-48.57748843810545</v>
+        <v>-49.23794825822814</v>
       </c>
       <c r="F102">
-        <v>-0.8742395681761286</v>
+        <v>-1.830991153223238</v>
       </c>
       <c r="G102">
-        <v>-5.506947991242225</v>
+        <v>-7.183785654520632</v>
       </c>
     </row>
   </sheetData>
